--- a/tools/excel/cis/cis-benchmark-google-workspace.xlsx
+++ b/tools/excel/cis/cis-benchmark-google-workspace.xlsx
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(L2) Ensure Super Admin account recovery is enabled</t>
+          <t>(L2) Ensure Super Admin account recovery is disabled</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
